--- a/product_selector_out/STM32F3 series.xlsx
+++ b/product_selector_out/STM32F3 series.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AD12" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE12" s="4" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE13" s="4" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>10, 9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AD14" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE14" s="4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE15" s="4" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE16" s="4" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AD17" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE17" s="4" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AD18" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE18" s="4" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>15, 18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="AD19" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE19" s="4" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="AD30" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE30" s="4" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="AD31" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE31" s="4" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>8, 9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="AD33" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE33" s="4" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AD34" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE34" s="4" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>8, 9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AD37" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE37" s="4" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AD38" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE38" s="4" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AD39" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE39" s="4" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="AD40" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE40" s="4" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="AD42" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE42" s="4" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="AD43" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AE43" s="4" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="AD44" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AE44" s="4" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="AD49" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE49" s="4" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="AD51" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE51" s="4" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="AD53" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE53" s="4" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="AD54" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AE54" s="4" t="inlineStr">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S55" s="4" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AD55" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE55" s="4" t="inlineStr">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="AD69" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AE69" s="4" t="inlineStr">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="R70" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S70" s="4" t="inlineStr">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="AD70" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE70" s="4" t="inlineStr">
@@ -24307,14 +24307,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
@@ -24337,9 +24337,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="6" t="inlineStr">
@@ -24392,9 +24392,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL12" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL12" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM12" s="9" t="inlineStr">
@@ -24634,14 +24634,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
@@ -24664,9 +24664,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="6" t="inlineStr">
@@ -24719,9 +24719,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM13" s="9" t="inlineStr">
@@ -24961,14 +24961,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
@@ -24991,9 +24991,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="6" t="inlineStr">
@@ -25046,9 +25046,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM14" s="9" t="inlineStr">
@@ -25288,14 +25288,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
@@ -25318,9 +25318,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="6" t="inlineStr">
@@ -25373,9 +25373,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL15" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL15" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM15" s="9" t="inlineStr">
@@ -25615,14 +25615,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
@@ -25645,9 +25645,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="6" t="inlineStr">
@@ -25700,9 +25700,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL16" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL16" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM16" s="9" t="inlineStr">
@@ -25942,14 +25942,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
@@ -25972,9 +25972,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="6" t="inlineStr">
@@ -26027,9 +26027,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL17" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM17" s="9" t="inlineStr">
@@ -26269,14 +26269,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
@@ -26299,9 +26299,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="6" t="inlineStr">
@@ -26354,9 +26354,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL18" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL18" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM18" s="9" t="inlineStr">
@@ -26596,14 +26596,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
@@ -26626,9 +26626,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="6" t="inlineStr">
@@ -26681,9 +26681,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL19" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL19" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM19" s="9" t="inlineStr">
@@ -30193,14 +30193,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W30" s="9" t="inlineStr">
@@ -30223,9 +30223,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA30" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB30" s="6" t="inlineStr">
@@ -30278,9 +30278,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL30" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM30" s="9" t="inlineStr">
@@ -30520,14 +30520,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W31" s="9" t="inlineStr">
@@ -30550,9 +30550,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA31" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB31" s="6" t="inlineStr">
@@ -30605,9 +30605,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL31" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM31" s="9" t="inlineStr">
@@ -30847,14 +30847,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W32" s="9" t="inlineStr">
@@ -30877,9 +30877,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA32" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB32" s="6" t="inlineStr">
@@ -30892,9 +30892,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD32" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE32" s="9" t="inlineStr">
@@ -30932,9 +30932,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL32" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM32" s="9" t="inlineStr">
@@ -31174,14 +31174,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
@@ -31204,9 +31204,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA33" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB33" s="6" t="inlineStr">
@@ -31259,9 +31259,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL33" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM33" s="9" t="inlineStr">
@@ -31501,14 +31501,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W34" s="9" t="inlineStr">
@@ -31531,9 +31531,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA34" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB34" s="6" t="inlineStr">
@@ -31586,9 +31586,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL34" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM34" s="9" t="inlineStr">
@@ -31828,14 +31828,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W35" s="9" t="inlineStr">
@@ -31858,9 +31858,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA35" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB35" s="6" t="inlineStr">
@@ -31873,9 +31873,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD35" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE35" s="9" t="inlineStr">
@@ -31913,9 +31913,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL35" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM35" s="9" t="inlineStr">
@@ -32482,14 +32482,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W37" s="9" t="inlineStr">
@@ -32512,9 +32512,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA37" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB37" s="6" t="inlineStr">
@@ -32567,9 +32567,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL37" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM37" s="9" t="inlineStr">
@@ -32839,9 +32839,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA38" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB38" s="6" t="inlineStr">
@@ -33136,14 +33136,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W39" s="9" t="inlineStr">
@@ -33166,9 +33166,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA39" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB39" s="6" t="inlineStr">
@@ -33221,9 +33221,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL39" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM39" s="9" t="inlineStr">
@@ -33463,14 +33463,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W40" s="9" t="inlineStr">
@@ -33493,9 +33493,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA40" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB40" s="6" t="inlineStr">
@@ -33548,9 +33548,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL40" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM40" s="9" t="inlineStr">
@@ -33820,9 +33820,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA41" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB41" s="6" t="inlineStr">
@@ -34147,9 +34147,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA42" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB42" s="6" t="inlineStr">
@@ -34474,9 +34474,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA43" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB43" s="6" t="inlineStr">
@@ -34801,9 +34801,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA44" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB44" s="6" t="inlineStr">
@@ -35782,9 +35782,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA47" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB47" s="6" t="inlineStr">
@@ -36406,14 +36406,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W49" s="9" t="inlineStr">
@@ -36436,9 +36436,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA49" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB49" s="6" t="inlineStr">
@@ -36491,9 +36491,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL49" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM49" s="9" t="inlineStr">
@@ -37060,14 +37060,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U51" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V51" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W51" s="9" t="inlineStr">
@@ -37090,9 +37090,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA51" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA51" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB51" s="6" t="inlineStr">
@@ -37145,9 +37145,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL51" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL51" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM51" s="9" t="inlineStr">
@@ -37714,14 +37714,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W53" s="9" t="inlineStr">
@@ -37744,9 +37744,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA53" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB53" s="6" t="inlineStr">
@@ -37799,9 +37799,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL53" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL53" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM53" s="9" t="inlineStr">
@@ -46784,7 +46784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -46889,7 +46889,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -46899,19 +46899,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334C6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -46921,7 +46921,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -46933,7 +46933,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -46943,7 +46943,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -46955,7 +46955,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -46977,7 +46977,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -46987,19 +46987,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -47009,19 +47009,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>summary row reads USART = 2 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -47043,7 +47043,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -47053,7 +47053,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -47065,7 +47065,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -47075,19 +47075,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -47097,19 +47097,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -47119,19 +47119,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 2 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -47141,7 +47141,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -47153,7 +47153,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -47163,19 +47163,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -47185,19 +47185,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -47214,12 +47214,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -47229,14 +47229,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -47258,7 +47258,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -47273,14 +47273,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -47302,7 +47302,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -47324,12 +47324,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -47339,19 +47339,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 2 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -47361,19 +47361,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -47383,19 +47383,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -47412,12 +47412,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -47427,19 +47427,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -47449,19 +47449,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -47471,19 +47471,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -47493,19 +47493,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -47515,19 +47515,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F398VE</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -47537,19 +47537,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F398VE</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -47559,19 +47559,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32F328C8</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -47581,19 +47581,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32F328C8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -47603,14 +47603,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32F318C8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -47632,7 +47632,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32F318C8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -47654,12 +47654,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32F318K8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -47669,19 +47669,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32F318K8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -47691,14 +47691,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32F358VC</t>
+          <t>STM32F398VE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -47713,14 +47713,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32F358VC</t>
+          <t>STM32F398VE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -47735,14 +47735,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32F358RC</t>
+          <t>STM32F328C8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -47757,14 +47757,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32F358RC</t>
+          <t>STM32F328C8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -47779,14 +47779,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32F378VC</t>
+          <t>STM32F318C8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -47808,7 +47808,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32F378VC</t>
+          <t>STM32F318C8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -47830,7 +47830,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32F358CC</t>
+          <t>STM32F318K8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -47852,7 +47852,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32F358CC</t>
+          <t>STM32F318K8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -47874,7 +47874,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32F378RC</t>
+          <t>STM32F358VC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -47896,7 +47896,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32F378RC</t>
+          <t>STM32F358VC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -47918,7 +47918,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32F378CC</t>
+          <t>STM32F358RC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -47940,7 +47940,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32F378CC</t>
+          <t>STM32F358RC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -47962,12 +47962,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32F301R8</t>
+          <t>STM32F378VC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -47977,19 +47977,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32F301C8</t>
+          <t>STM32F378VC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -47999,19 +47999,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32F301K8</t>
+          <t>STM32F358CC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -48021,19 +48021,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32F301C6</t>
+          <t>STM32F358CC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -48043,19 +48043,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32F301R6</t>
+          <t>STM32F378RC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -48065,19 +48065,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32F301K6</t>
+          <t>STM32F378RC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -48087,14 +48087,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32F302VC</t>
+          <t>STM32F378CC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -48116,7 +48116,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32F302VC</t>
+          <t>STM32F378CC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -48138,7 +48138,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32F302C6</t>
+          <t>STM32F301R8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -48153,14 +48153,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F301C8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -48175,14 +48175,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F301K8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -48197,14 +48197,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F301C6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -48219,14 +48219,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32F302VD</t>
+          <t>STM32F301R6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -48241,14 +48241,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F301K6</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -48263,19 +48263,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F302VC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -48285,19 +48285,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32F302ZE</t>
+          <t>STM32F302VC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -48307,19 +48307,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32F302CB</t>
+          <t>STM32F302C6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -48329,19 +48329,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32F302CB</t>
+          <t>STM32F302RE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -48351,19 +48351,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32F302RB</t>
+          <t>STM32F302K6</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -48373,19 +48373,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32F302RB</t>
+          <t>STM32F302R6</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -48395,14 +48395,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32F302VE</t>
+          <t>STM32F302VD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -48424,12 +48424,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32F302VB</t>
+          <t>STM32F302RD</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -48439,19 +48439,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32F302VB</t>
+          <t>STM32F302ZD</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -48461,14 +48461,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32F302C8</t>
+          <t>STM32F302ZE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -48483,14 +48483,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32F302CC</t>
+          <t>STM32F302CB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -48512,7 +48512,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32F302CC</t>
+          <t>STM32F302CB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -48534,12 +48534,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32F302K8</t>
+          <t>STM32F302RB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -48549,19 +48549,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32F302RC</t>
+          <t>STM32F302RB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -48578,12 +48578,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32F302RC</t>
+          <t>STM32F302VE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -48593,19 +48593,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32F302R8</t>
+          <t>STM32F302VB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -48615,19 +48615,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F302VB</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -48637,19 +48637,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F302C8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -48659,19 +48659,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F302CC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -48681,19 +48681,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F302CC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -48703,14 +48703,14 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32F303VD</t>
+          <t>STM32F302K8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -48725,19 +48725,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32F303VD</t>
+          <t>STM32F302RC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -48747,19 +48747,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32F303K8</t>
+          <t>STM32F302RC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -48776,12 +48776,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32F303K8</t>
+          <t>STM32F302R8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -48791,19 +48791,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32F303VC</t>
+          <t>STM32F303ZD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -48813,19 +48813,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32F303VC</t>
+          <t>STM32F303ZD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -48835,19 +48835,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32F303C8</t>
+          <t>STM32F303RD</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -48857,19 +48857,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32F303C8</t>
+          <t>STM32F303RD</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -48879,19 +48879,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32F303RC</t>
+          <t>STM32F303VD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -48901,19 +48901,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32F303RC</t>
+          <t>STM32F303VD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -48923,14 +48923,14 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32F303CC</t>
+          <t>STM32F303K8</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -48952,7 +48952,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32F303CC</t>
+          <t>STM32F303K8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -48974,7 +48974,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32F303CB</t>
+          <t>STM32F303VC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -48996,7 +48996,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32F303CB</t>
+          <t>STM32F303VC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -49018,12 +49018,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32F303VE</t>
+          <t>STM32F303C8</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -49033,19 +49033,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32F303VE</t>
+          <t>STM32F303C8</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -49055,14 +49055,14 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32F303RB</t>
+          <t>STM32F303RC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -49084,7 +49084,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32F303RB</t>
+          <t>STM32F303RC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -49106,7 +49106,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32F303R6</t>
+          <t>STM32F303CC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -49128,7 +49128,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32F303R6</t>
+          <t>STM32F303CC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -49150,7 +49150,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32F303VB</t>
+          <t>STM32F303CB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -49172,7 +49172,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32F303VB</t>
+          <t>STM32F303CB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -49194,12 +49194,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32F303K6</t>
+          <t>STM32F303VE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -49209,19 +49209,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32F303K6</t>
+          <t>STM32F303VE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -49231,14 +49231,14 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32F303C6</t>
+          <t>STM32F303RB</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49260,7 +49260,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32F303C6</t>
+          <t>STM32F303RB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49282,12 +49282,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32F303ZE</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -49297,19 +49297,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32F303ZE</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -49319,19 +49319,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32F303RE</t>
+          <t>STM32F303VB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -49341,19 +49341,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32F303RE</t>
+          <t>STM32F303VB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -49363,14 +49363,14 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32F303R8</t>
+          <t>STM32F303K6</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -49392,7 +49392,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32F303R8</t>
+          <t>STM32F303K6</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -49414,7 +49414,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32F373C8</t>
+          <t>STM32F303C6</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -49436,7 +49436,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32F373C8</t>
+          <t>STM32F303C6</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -49458,12 +49458,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32F373R8</t>
+          <t>STM32F303ZE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -49473,19 +49473,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32F373R8</t>
+          <t>STM32F303ZE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -49495,19 +49495,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32F373V8</t>
+          <t>STM32F303RE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -49517,19 +49517,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32F373V8</t>
+          <t>STM32F303RE</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -49539,14 +49539,14 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32F373VC</t>
+          <t>STM32F303R8</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -49568,7 +49568,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32F373VC</t>
+          <t>STM32F303R8</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -49590,7 +49590,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32F373CB</t>
+          <t>STM32F373C8</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -49612,7 +49612,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32F373CB</t>
+          <t>STM32F373C8</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -49634,7 +49634,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32F373RC</t>
+          <t>STM32F373R8</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -49656,7 +49656,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32F373RC</t>
+          <t>STM32F373R8</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -49678,7 +49678,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32F373CC</t>
+          <t>STM32F373V8</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -49700,7 +49700,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32F373CC</t>
+          <t>STM32F373V8</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -49722,7 +49722,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32F373RB</t>
+          <t>STM32F373VC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -49744,7 +49744,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32F373RB</t>
+          <t>STM32F373VC</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -49766,7 +49766,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32F373VB</t>
+          <t>STM32F373CB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -49788,20 +49788,196 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>STM32F373CB</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>STM32F373RC</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>STM32F373RC</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>STM32F373CC</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>STM32F373CC</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>STM32F373RB</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>STM32F373RB</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
           <t>STM32F373VB</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>STM32F373VB</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
         <is>
           <t>Timers (32-bit) typ</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32F3 series.xlsx
+++ b/product_selector_out/STM32F3 series.xlsx
@@ -1647,7 +1647,7 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1759,214 +1759,214 @@
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
+          <t>10, 9</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD14" s="4" t="inlineStr">
+        <is>
+          <t>24, 25</t>
+        </is>
+      </c>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG14" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL14" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN14" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AT14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AU14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AV14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AW14" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AX14" s="4" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="AY14" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ14" s="4" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="BA14" s="4" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="BB14" s="4" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="BC14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BE14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BF14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BG14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BH14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BI14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BJ14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BK14" s="4" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="W14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB14" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG14" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH14" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ14" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AL14" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AN14" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AO14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AS14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AT14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AU14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AV14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AW14" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AX14" s="4" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="AY14" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ14" s="4" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="BA14" s="4" t="inlineStr">
-        <is>
-          <t>-40</t>
-        </is>
-      </c>
-      <c r="BB14" s="4" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="BC14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BD14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BE14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BF14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BG14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BH14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BI14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BJ14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BK14" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="BL14" s="4" t="inlineStr">
         <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -18416,7 +18416,7 @@
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S65" s="4" t="inlineStr">
@@ -18521,7 +18521,7 @@
       </c>
       <c r="AM65" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN65" s="4" t="inlineStr">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f303c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
     </row>
@@ -20378,7 +20378,7 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S71" s="4" t="inlineStr">
@@ -20483,7 +20483,7 @@
       </c>
       <c r="AM71" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN71" s="4" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f303c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
     </row>
@@ -24549,19 +24549,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -24619,14 +24619,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -24634,14 +24634,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
@@ -24664,9 +24664,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB13" s="6" t="inlineStr">
@@ -24679,9 +24679,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE13" s="9" t="inlineStr">
@@ -24694,14 +24694,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AH13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AG13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AI13" s="9" t="inlineStr">
@@ -24709,9 +24709,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AJ13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AJ13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK13" s="9" t="inlineStr">
@@ -24719,9 +24719,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AL13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM13" s="9" t="inlineStr">
@@ -24794,14 +24794,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC13" s="9" t="inlineStr">
@@ -24854,9 +24854,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM13" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -24876,19 +24876,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -24946,14 +24946,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -24961,14 +24961,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
@@ -24991,9 +24991,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB14" s="6" t="inlineStr">
@@ -25006,9 +25006,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE14" s="9" t="inlineStr">
@@ -25021,14 +25021,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AH14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AG14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AI14" s="9" t="inlineStr">
@@ -25036,9 +25036,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AJ14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AJ14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK14" s="9" t="inlineStr">
@@ -25046,9 +25046,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AL14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM14" s="9" t="inlineStr">
@@ -25121,14 +25121,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC14" s="9" t="inlineStr">
@@ -25181,9 +25181,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM14" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -25857,19 +25857,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -25927,14 +25927,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -25942,14 +25942,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="U17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
@@ -25972,9 +25972,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB17" s="6" t="inlineStr">
@@ -25987,9 +25987,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE17" s="9" t="inlineStr">
@@ -26002,14 +26002,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AH17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AG17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AH17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AI17" s="9" t="inlineStr">
@@ -26017,9 +26017,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AJ17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AJ17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK17" s="9" t="inlineStr">
@@ -26027,9 +26027,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AL17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM17" s="9" t="inlineStr">
@@ -26102,14 +26102,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC17" s="9" t="inlineStr">
@@ -26162,9 +26162,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM17" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -32899,9 +32899,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM38" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN38" s="6" t="inlineStr">
@@ -33880,9 +33880,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM41" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN41" s="6" t="inlineStr">
@@ -34207,9 +34207,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM42" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN42" s="6" t="inlineStr">
@@ -34534,9 +34534,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM43" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN43" s="6" t="inlineStr">
@@ -34861,9 +34861,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM44" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN44" s="6" t="inlineStr">
@@ -35842,9 +35842,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM47" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN47" s="6" t="inlineStr">
@@ -38131,9 +38131,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM54" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN54" s="6" t="inlineStr">
@@ -38458,9 +38458,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM55" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM55" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN55" s="6" t="inlineStr">
@@ -38785,9 +38785,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM56" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN56" s="6" t="inlineStr">
@@ -41074,9 +41074,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM63" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM63" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN63" s="6" t="inlineStr">
@@ -41553,9 +41553,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -41563,249 +41563,249 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="M65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="N65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="O65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R65" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AB65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AC65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD65" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="L65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="M65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="N65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="O65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R65" s="7" t="inlineStr">
+      <c r="AE65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AH65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AI65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL65" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AM65" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AN65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AO65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AQ65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AR65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AS65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AT65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW65" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AX65" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AY65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BA65" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BB65" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AB65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AC65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AE65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AH65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AI65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AM65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AO65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AQ65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AR65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AS65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AT65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV65" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="BA65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="BB65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
         </is>
       </c>
       <c r="BC65" s="9" t="inlineStr">
@@ -43036,9 +43036,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM69" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN69" s="6" t="inlineStr">
@@ -43363,9 +43363,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM70" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN70" s="6" t="inlineStr">
@@ -43515,9 +43515,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -43525,249 +43525,249 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="M71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="N71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="O71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R71" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S71" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AB71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AC71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD71" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="L71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="M71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="N71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="O71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R71" s="7" t="inlineStr">
+      <c r="AE71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AH71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AI71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL71" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AM71" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AN71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AO71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AQ71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AR71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AS71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AT71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW71" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AX71" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AY71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BA71" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BB71" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S71" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AB71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AC71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AE71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AH71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AI71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AM71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AO71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AQ71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AR71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AS71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AT71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV71" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="BA71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="BB71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
         </is>
       </c>
       <c r="BC71" s="9" t="inlineStr">
@@ -46784,7 +46784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -46928,7 +46928,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -46943,14 +46943,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -46972,7 +46972,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -46994,7 +46994,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -47009,14 +47009,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>summary row reads USART = 2 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -47038,7 +47038,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -47060,7 +47060,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -47082,7 +47082,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -47104,7 +47104,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -47126,7 +47126,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -47148,7 +47148,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -47163,14 +47163,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -47192,7 +47192,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -47214,7 +47214,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -47236,7 +47236,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -47258,7 +47258,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -47273,14 +47273,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -47302,7 +47302,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -47324,7 +47324,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -47339,14 +47339,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>summary row reads USART = 2 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -47368,12 +47368,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F398VE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -47383,19 +47383,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F398VE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -47405,19 +47405,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F328C8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -47427,19 +47427,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F328C8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -47449,19 +47449,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F318C8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -47471,19 +47471,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F318C8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -47493,14 +47493,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F318K8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -47522,7 +47522,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F318K8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -47544,12 +47544,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F358VC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -47559,19 +47559,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F358VC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -47581,19 +47581,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F358RC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -47603,19 +47603,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F358RC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -47632,12 +47632,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F378VC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -47654,12 +47654,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F378VC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -47669,19 +47669,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F358CC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -47691,19 +47691,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32F398VE</t>
+          <t>STM32F358CC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -47713,19 +47713,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32F398VE</t>
+          <t>STM32F378RC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -47735,19 +47735,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32F328C8</t>
+          <t>STM32F378RC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -47757,19 +47757,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32F328C8</t>
+          <t>STM32F378CC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -47779,19 +47779,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32F318C8</t>
+          <t>STM32F378CC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -47808,12 +47808,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32F318C8</t>
+          <t>STM32F301R8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -47823,19 +47823,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32F318K8</t>
+          <t>STM32F301C8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -47845,19 +47845,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32F318K8</t>
+          <t>STM32F301K8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -47867,19 +47867,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32F358VC</t>
+          <t>STM32F301C6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -47889,19 +47889,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32F358VC</t>
+          <t>STM32F301R6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -47911,19 +47911,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32F358RC</t>
+          <t>STM32F301K6</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -47933,19 +47933,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32F358RC</t>
+          <t>STM32F302VC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -47962,12 +47962,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32F378VC</t>
+          <t>STM32F302VC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -47984,12 +47984,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32F378VC</t>
+          <t>STM32F302C6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -47999,19 +47999,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32F358CC</t>
+          <t>STM32F302RE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -48021,19 +48021,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32F358CC</t>
+          <t>STM32F302K6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -48043,19 +48043,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32F378RC</t>
+          <t>STM32F302R6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -48065,19 +48065,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32F378RC</t>
+          <t>STM32F302VD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -48087,19 +48087,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32F378CC</t>
+          <t>STM32F302RD</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -48109,19 +48109,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32F378CC</t>
+          <t>STM32F302ZD</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -48131,14 +48131,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32F301R8</t>
+          <t>STM32F302ZE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -48153,19 +48153,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32F301C8</t>
+          <t>STM32F302CB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -48175,19 +48175,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32F301K8</t>
+          <t>STM32F302CB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -48197,19 +48197,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32F301C6</t>
+          <t>STM32F302RB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -48219,19 +48219,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32F301R6</t>
+          <t>STM32F302RB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -48241,14 +48241,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32F301K6</t>
+          <t>STM32F302VE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -48263,14 +48263,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 2. STM32F301x6/8 device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32F302VC</t>
+          <t>STM32F302VB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -48292,7 +48292,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32F302VC</t>
+          <t>STM32F302VB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -48314,7 +48314,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32F302C6</t>
+          <t>STM32F302C8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -48336,12 +48336,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32F302RE</t>
+          <t>STM32F302CC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -48351,19 +48351,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32F302K6</t>
+          <t>STM32F302CC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -48373,14 +48373,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32F302R6</t>
+          <t>STM32F302K8</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -48395,19 +48395,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32F302VD</t>
+          <t>STM32F302RC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -48417,19 +48417,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32F302RD</t>
+          <t>STM32F302RC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -48439,14 +48439,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32F302ZD</t>
+          <t>STM32F302R8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -48461,14 +48461,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32F302ZE</t>
+          <t>STM32F303ZD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -48483,19 +48483,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32F302CB</t>
+          <t>STM32F303ZD</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -48505,19 +48505,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32F302CB</t>
+          <t>STM32F303RD</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -48527,19 +48527,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32F302RB</t>
+          <t>STM32F303RD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -48549,19 +48549,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32F302RB</t>
+          <t>STM32F303VD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -48571,19 +48571,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32F302VE</t>
+          <t>STM32F303VD</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -48593,14 +48593,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32F302VB</t>
+          <t>STM32F303K8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -48622,7 +48622,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32F302VB</t>
+          <t>STM32F303K8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -48644,12 +48644,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32F302C8</t>
+          <t>STM32F303VC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -48659,19 +48659,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32F302CC</t>
+          <t>STM32F303VC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -48688,12 +48688,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32F302CC</t>
+          <t>STM32F303C8</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -48710,12 +48710,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32F302K8</t>
+          <t>STM32F303C8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -48725,14 +48725,14 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32F302RC</t>
+          <t>STM32F303RC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -48754,7 +48754,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32F302RC</t>
+          <t>STM32F303RC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -48776,12 +48776,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32F302R8</t>
+          <t>STM32F303CC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -48791,19 +48791,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 2. STM32F302x6/8 device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F303CC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -48813,19 +48813,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F303CB</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -48835,19 +48835,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F303CB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -48857,19 +48857,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F303VE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -48879,19 +48879,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32F303VD</t>
+          <t>STM32F303VE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -48901,19 +48901,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32F303VD</t>
+          <t>STM32F303RB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -48923,19 +48923,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32F303K8</t>
+          <t>STM32F303RB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -48952,12 +48952,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32F303K8</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -48967,19 +48967,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32F303VC</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -48989,19 +48989,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32F303VC</t>
+          <t>STM32F303VB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -49018,12 +49018,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32F303C8</t>
+          <t>STM32F303VB</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -49040,12 +49040,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32F303C8</t>
+          <t>STM32F303K6</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -49062,12 +49062,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32F303RC</t>
+          <t>STM32F303K6</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -49084,12 +49084,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32F303RC</t>
+          <t>STM32F303C6</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -49106,12 +49106,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32F303CC</t>
+          <t>STM32F303C6</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -49128,12 +49128,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32F303CC</t>
+          <t>STM32F303ZE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -49143,19 +49143,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32F303CB</t>
+          <t>STM32F303ZE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -49165,19 +49165,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32F303CB</t>
+          <t>STM32F303RE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -49187,19 +49187,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32F303VE</t>
+          <t>STM32F303RE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -49209,19 +49209,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP100, UFBGA100, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32F303VE</t>
+          <t>STM32F303R8</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -49231,19 +49231,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32F303RB</t>
+          <t>STM32F303R8</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -49253,19 +49253,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32F303RB</t>
+          <t>STM32F373C8</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -49282,12 +49282,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32F303R6</t>
+          <t>STM32F373C8</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -49304,12 +49304,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32F303R6</t>
+          <t>STM32F373R8</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -49326,12 +49326,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32F303VB</t>
+          <t>STM32F373R8</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -49348,12 +49348,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32F303VB</t>
+          <t>STM32F373V8</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -49370,12 +49370,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32F303K6</t>
+          <t>STM32F373V8</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -49392,12 +49392,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32F303K6</t>
+          <t>STM32F373VC</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -49414,12 +49414,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32F303C6</t>
+          <t>STM32F373VC</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -49436,12 +49436,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32F303C6</t>
+          <t>STM32F373CB</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -49458,12 +49458,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32F303ZE</t>
+          <t>STM32F373CB</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -49473,19 +49473,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32F303ZE</t>
+          <t>STM32F373RC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -49495,19 +49495,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32F303RE</t>
+          <t>STM32F373RC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -49517,19 +49517,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32F303RE</t>
+          <t>STM32F373CC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -49539,19 +49539,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32F303R8</t>
+          <t>STM32F373CC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -49568,12 +49568,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32F303R8</t>
+          <t>STM32F373RB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -49590,12 +49590,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32F373C8</t>
+          <t>STM32F373RB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -49612,12 +49612,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32F373C8</t>
+          <t>STM32F373VB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -49634,12 +49634,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32F373R8</t>
+          <t>STM32F373VB</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -49648,336 +49648,6 @@
         </is>
       </c>
       <c r="D130" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>STM32F373R8</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>STM32F373V8</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>STM32F373V8</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>STM32F373VC</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>STM32F373VC</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>STM32F373CB</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>STM32F373CB</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>STM32F373RC</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>STM32F373RC</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>STM32F373CC</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>STM32F373CC</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>STM32F373RB</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>STM32F373RB</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>STM32F373VB</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>STM32F373VB</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
         <is>
           <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32F3 series.xlsx
+++ b/product_selector_out/STM32F3 series.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM80"/>
+  <dimension ref="A1:BN80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.51953125" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
         </is>
       </c>
@@ -1650,6 +1662,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1977,6 +1994,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
         </is>
       </c>
@@ -2958,6 +2990,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f398ve.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f328c8.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f318c8.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f318c8.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f358cc.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f358cc.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f378cc.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f358cc.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f378cc.pdf</t>
         </is>
       </c>
@@ -6879,6 +6971,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f378cc.pdf</t>
         </is>
       </c>
@@ -7206,6 +7303,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f301c6.pdf</t>
         </is>
       </c>
@@ -7533,6 +7635,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f301c6.pdf</t>
         </is>
       </c>
@@ -7860,6 +7967,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f301c6.pdf</t>
         </is>
       </c>
@@ -8187,6 +8299,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f301c6.pdf</t>
         </is>
       </c>
@@ -8514,6 +8631,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f301c6.pdf</t>
         </is>
       </c>
@@ -8841,6 +8963,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f301c6.pdf</t>
         </is>
       </c>
@@ -9168,6 +9295,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302cb.pdf</t>
         </is>
       </c>
@@ -9495,6 +9627,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302c6.pdf</t>
         </is>
       </c>
@@ -9822,6 +9959,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302rd.pdf</t>
         </is>
       </c>
@@ -10149,6 +10291,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302c6.pdf</t>
         </is>
       </c>
@@ -10476,6 +10623,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302c6.pdf</t>
         </is>
       </c>
@@ -10803,6 +10955,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302rd.pdf</t>
         </is>
       </c>
@@ -11130,6 +11287,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302rd.pdf</t>
         </is>
       </c>
@@ -11457,6 +11619,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302rd.pdf</t>
         </is>
       </c>
@@ -11784,6 +11951,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302rd.pdf</t>
         </is>
       </c>
@@ -12111,6 +12283,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302cb.pdf</t>
         </is>
       </c>
@@ -12438,6 +12615,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302cb.pdf</t>
         </is>
       </c>
@@ -12765,6 +12947,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302rd.pdf</t>
         </is>
       </c>
@@ -13092,6 +13279,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302cb.pdf</t>
         </is>
       </c>
@@ -13419,6 +13611,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302c6.pdf</t>
         </is>
       </c>
@@ -13746,6 +13943,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302cb.pdf</t>
         </is>
       </c>
@@ -14073,6 +14275,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302c6.pdf</t>
         </is>
       </c>
@@ -14400,6 +14607,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302cb.pdf</t>
         </is>
       </c>
@@ -14727,6 +14939,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302c6.pdf</t>
         </is>
       </c>
@@ -15054,6 +15271,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -15381,6 +15603,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -15708,6 +15935,11 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -16035,6 +16267,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303c6.pdf</t>
         </is>
       </c>
@@ -16362,6 +16599,11 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303cb.pdf</t>
         </is>
       </c>
@@ -16689,6 +16931,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303c6.pdf</t>
         </is>
       </c>
@@ -17016,6 +17263,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303cb.pdf</t>
         </is>
       </c>
@@ -17343,6 +17595,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303cb.pdf</t>
         </is>
       </c>
@@ -17670,6 +17927,11 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303cb.pdf</t>
         </is>
       </c>
@@ -17997,6 +18259,11 @@
       </c>
       <c r="BM63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -18324,6 +18591,11 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303cb.pdf</t>
         </is>
       </c>
@@ -18651,6 +18923,11 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -18978,6 +19255,11 @@
       </c>
       <c r="BM66" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303cb.pdf</t>
         </is>
       </c>
@@ -19305,6 +19587,11 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303c6.pdf</t>
         </is>
       </c>
@@ -19632,6 +19919,11 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303c6.pdf</t>
         </is>
       </c>
@@ -19959,6 +20251,11 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -20286,6 +20583,11 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN70" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -20613,6 +20915,11 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -20940,6 +21247,11 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN72" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f373c8.pdf</t>
         </is>
       </c>
@@ -21267,6 +21579,11 @@
       </c>
       <c r="BM73" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f373c8.pdf</t>
         </is>
       </c>
@@ -21594,6 +21911,11 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f373c8.pdf</t>
         </is>
       </c>
@@ -21921,6 +22243,11 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f373c8.pdf</t>
         </is>
       </c>
@@ -22248,6 +22575,11 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f373c8.pdf</t>
         </is>
       </c>
@@ -22575,6 +22907,11 @@
       </c>
       <c r="BM77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f373c8.pdf</t>
         </is>
       </c>
@@ -22902,6 +23239,11 @@
       </c>
       <c r="BM78" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f373c8.pdf</t>
         </is>
       </c>
@@ -23229,6 +23571,11 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f373c8.pdf</t>
         </is>
       </c>
@@ -23556,12 +23903,17 @@
       </c>
       <c r="BM80" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f373c8.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -23582,16 +23934,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -23604,6 +23954,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -23623,7 +23974,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -23709,7 +24062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM80"/>
+  <dimension ref="A1:BN80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -23777,6 +24130,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24110,6 +24464,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -24205,6 +24564,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -24527,7 +24887,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24859,6 +25224,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN13" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -25186,6 +25556,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN14" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -25508,7 +25883,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25835,7 +26215,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26167,6 +26552,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN17" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -26489,7 +26879,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26816,7 +27211,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27143,7 +27543,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27470,7 +27875,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27797,7 +28207,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28124,7 +28539,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28451,7 +28871,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28778,7 +29203,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29105,7 +29535,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29432,7 +29867,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29759,7 +30199,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30086,7 +30531,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30413,7 +30863,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30740,7 +31195,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31067,7 +31527,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31394,7 +31859,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31721,7 +32191,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32048,7 +32523,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32375,7 +32855,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32702,7 +33187,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33029,7 +33519,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33356,7 +33851,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33683,7 +34183,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34010,7 +34515,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34337,7 +34847,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34664,7 +35179,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34991,7 +35511,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35318,7 +35843,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35645,7 +36175,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35972,7 +36507,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36299,7 +36839,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36626,7 +37171,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36953,7 +37503,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37280,7 +37835,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37607,7 +38167,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37934,7 +38499,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38261,7 +38831,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38588,7 +39163,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38915,7 +39495,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
+      <c r="BM56" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39242,7 +39827,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39569,7 +40159,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
+      <c r="BM58" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39896,7 +40491,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40223,7 +40823,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40550,7 +41155,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40877,7 +41487,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41204,7 +41819,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM63" s="6" t="inlineStr">
+      <c r="BM63" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41531,7 +42151,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
+      <c r="BM64" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41858,7 +42483,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
+      <c r="BM65" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42185,7 +42815,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM66" s="6" t="inlineStr">
+      <c r="BM66" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42512,7 +43147,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
+      <c r="BM67" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42839,7 +43479,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
+      <c r="BM68" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43166,7 +43811,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="6" t="inlineStr">
+      <c r="BM69" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43493,7 +44143,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="6" t="inlineStr">
+      <c r="BM70" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN70" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43820,7 +44475,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="6" t="inlineStr">
+      <c r="BM71" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44147,7 +44807,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
+      <c r="BM72" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN72" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44474,7 +45139,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM73" s="6" t="inlineStr">
+      <c r="BM73" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44801,7 +45471,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
+      <c r="BM74" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45128,7 +45803,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="6" t="inlineStr">
+      <c r="BM75" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45455,7 +46135,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
+      <c r="BM76" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45782,7 +46467,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM77" s="6" t="inlineStr">
+      <c r="BM77" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46109,7 +46799,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM78" s="6" t="inlineStr">
+      <c r="BM78" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46436,7 +47131,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="6" t="inlineStr">
+      <c r="BM79" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46763,7 +47463,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM80" s="6" t="inlineStr">
+      <c r="BM80" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46771,8 +47476,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
